--- a/accountant-skill/data/output/Jan2026/adjusting_entries_Jan2026.xlsx
+++ b/accountant-skill/data/output/Jan2026/adjusting_entries_Jan2026.xlsx
@@ -112,7 +112,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -129,11 +129,42 @@
     <border>
       <bottom style="double"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <bottom style="medium"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -172,6 +203,33 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -544,12 +602,12 @@
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -580,6 +638,9 @@
           <t>ENTRIES BY TYPE</t>
         </is>
       </c>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="18" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -609,10 +670,10 @@
           <t>Depreciation</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="19" t="n">
         <v>54750</v>
       </c>
       <c r="D7" s="7" t="n">
@@ -625,10 +686,10 @@
           <t>Bank Recon</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B8" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="19" t="n">
         <v>33000</v>
       </c>
       <c r="D8" s="7" t="n">
@@ -636,88 +697,103 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n">
+      <c r="B9" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="21" t="n">
         <v>87750</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>87750</v>
       </c>
+      <c r="E9" s="22" t="n"/>
+      <c r="F9" s="22" t="n"/>
+      <c r="G9" s="22" t="n"/>
+      <c r="H9" s="22" t="n"/>
     </row>
     <row r="10"/>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="23" t="inlineStr">
         <is>
           <t>VALIDATION</t>
         </is>
       </c>
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="17" t="n"/>
+      <c r="D11" s="18" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="24" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="24" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>Total Debits = Total Credits</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>87,750.00 = 87,750.00</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C13" s="25" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="22" t="n"/>
+      <c r="F13" s="22" t="n"/>
+      <c r="G13" s="22" t="n"/>
+      <c r="H13" s="22" t="n"/>
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="23" t="inlineStr">
         <is>
           <t>ALL ENTRIES</t>
         </is>
       </c>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="18" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="24" t="inlineStr">
         <is>
           <t>Reference</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="24" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="24" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="24" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
@@ -847,10 +923,10 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="44" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
@@ -882,64 +958,71 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>PER-ASSET DETAIL</t>
         </is>
       </c>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
+      <c r="G5" s="17" t="n"/>
+      <c r="H5" s="18" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="24" t="inlineStr">
         <is>
           <t>Asset ID</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="24" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="24" t="inlineStr">
         <is>
           <t>Cost</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="24" t="inlineStr">
         <is>
           <t>Salvage Value</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="24" t="inlineStr">
         <is>
           <t>Useful Life (yrs)</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="24" t="inlineStr">
         <is>
           <t>Annual Depr.</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="24" t="inlineStr">
         <is>
           <t>Monthly Depr.</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="J6" s="24" t="inlineStr">
         <is>
           <t>Depr. Account</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="K6" s="24" t="inlineStr">
         <is>
           <t>Accum. Depr. Account</t>
         </is>
@@ -1322,14 +1405,14 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>Total Monthly Depreciation</t>
         </is>
       </c>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
+      <c r="B15" s="26" t="n"/>
+      <c r="C15" s="26" t="n"/>
+      <c r="D15" s="26" t="n"/>
       <c r="E15" s="9" t="n"/>
       <c r="F15" s="9" t="n"/>
       <c r="G15" s="9" t="n"/>
@@ -1337,58 +1420,67 @@
       <c r="I15" s="9" t="n">
         <v>54750</v>
       </c>
+      <c r="J15" s="22" t="n"/>
+      <c r="K15" s="22" t="n"/>
     </row>
     <row r="16"/>
     <row r="17"/>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="23" t="inlineStr">
         <is>
           <t>JOURNAL ENTRIES (grouped by asset category)</t>
         </is>
       </c>
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="17" t="n"/>
+      <c r="E18" s="17" t="n"/>
+      <c r="F18" s="17" t="n"/>
+      <c r="G18" s="17" t="n"/>
+      <c r="H18" s="18" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="24" t="inlineStr">
         <is>
           <t>Reference</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="24" t="inlineStr">
         <is>
           <t>Debit Account</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="24" t="inlineStr">
         <is>
           <t>Dr Code</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F19" s="24" t="inlineStr">
         <is>
           <t>Debit Amount</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G19" s="24" t="inlineStr">
         <is>
           <t>Credit Account</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="H19" s="24" t="inlineStr">
         <is>
           <t>Cr Code</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="I19" s="24" t="inlineStr">
         <is>
           <t>Credit Amount</t>
         </is>
@@ -1524,14 +1616,14 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>Total Depreciation</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="9" t="n"/>
-      <c r="D23" s="9" t="n"/>
+      <c r="B23" s="26" t="n"/>
+      <c r="C23" s="26" t="n"/>
+      <c r="D23" s="26" t="n"/>
       <c r="E23" s="9" t="n"/>
       <c r="F23" s="9" t="n">
         <v>54750</v>
@@ -1541,6 +1633,8 @@
       <c r="I23" s="9" t="n">
         <v>54750</v>
       </c>
+      <c r="J23" s="22" t="n"/>
+      <c r="K23" s="22" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1564,15 +1658,15 @@
   <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -1747,21 +1841,21 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B8" s="9" t="n"/>
-      <c r="C8" s="9" t="n"/>
-      <c r="D8" s="9" t="n"/>
-      <c r="E8" s="9" t="n"/>
-      <c r="F8" s="9" t="n"/>
+      <c r="B8" s="26" t="n"/>
+      <c r="C8" s="26" t="n"/>
+      <c r="D8" s="26" t="n"/>
+      <c r="E8" s="26" t="n"/>
+      <c r="F8" s="26" t="n"/>
       <c r="G8" s="9" t="n">
         <v>33000</v>
       </c>
-      <c r="H8" s="9" t="n"/>
-      <c r="I8" s="9" t="n"/>
+      <c r="H8" s="26" t="n"/>
+      <c r="I8" s="26" t="n"/>
       <c r="J8" s="9" t="n">
         <v>33000</v>
       </c>
@@ -1786,14 +1880,14 @@
   <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1922,19 +2016,20 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B10" s="9" t="n"/>
+      <c r="B10" s="26" t="n"/>
       <c r="C10" s="9" t="n"/>
-      <c r="D10" s="9" t="n"/>
-      <c r="E10" s="9" t="n"/>
-      <c r="F10" s="9" t="n"/>
+      <c r="D10" s="26" t="n"/>
+      <c r="E10" s="26" t="n"/>
+      <c r="F10" s="26" t="n"/>
       <c r="G10" s="9" t="n">
         <v>205000</v>
       </c>
+      <c r="H10" s="22" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1957,14 +2052,14 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2064,19 +2159,20 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n"/>
+      <c r="B9" s="26" t="n"/>
       <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="9" t="n"/>
-      <c r="F9" s="9" t="n"/>
+      <c r="D9" s="26" t="n"/>
+      <c r="E9" s="26" t="n"/>
+      <c r="F9" s="26" t="n"/>
       <c r="G9" s="9" t="n">
         <v>20000</v>
       </c>
+      <c r="H9" s="22" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2098,6 +2194,16 @@
   </sheetPr>
   <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -2120,15 +2226,22 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>Materials issued to production are recorded via inventory sub-ledgers. Cost of materials used flows to COGS accounts.</t>
         </is>
       </c>
-    </row>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="18" t="n"/>
+    </row>
+    <row r="6"/>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>No inventory sub-ledger data found for this period.</t>
         </is>
@@ -2155,17 +2268,17 @@
   <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="29" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="44" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="52" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2513,39 +2626,39 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>TOTALS</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n"/>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="9" t="n"/>
-      <c r="F11" s="9" t="n"/>
+      <c r="B11" s="26" t="n"/>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="26" t="n"/>
+      <c r="E11" s="26" t="n"/>
+      <c r="F11" s="26" t="n"/>
       <c r="G11" s="9" t="n">
         <v>87750</v>
       </c>
-      <c r="H11" s="9" t="n"/>
-      <c r="I11" s="9" t="n"/>
+      <c r="H11" s="26" t="n"/>
+      <c r="I11" s="26" t="n"/>
       <c r="J11" s="9" t="n">
         <v>87750</v>
       </c>
-      <c r="K11" s="9" t="n"/>
+      <c r="K11" s="26" t="n"/>
     </row>
     <row r="12"/>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Double-Entry Check</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>Dr 87,750.00 = Cr 87,750.00</t>
         </is>
       </c>
-      <c r="G13" s="11" t="inlineStr">
+      <c r="G13" s="27" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2571,14 +2684,14 @@
   <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2675,7 +2788,7 @@
       <c r="G6" s="7" t="n">
         <v>1435500</v>
       </c>
-      <c r="H6" s="15" t="n">
+      <c r="H6" s="14" t="n">
         <v>-0.002085505735140772</v>
       </c>
     </row>
@@ -2709,7 +2822,7 @@
       <c r="G7" s="7" t="n">
         <v>518750</v>
       </c>
-      <c r="H7" s="15" t="n">
+      <c r="H7" s="7" t="n">
         <v>0.0375</v>
       </c>
     </row>
@@ -2743,7 +2856,7 @@
       <c r="G8" s="7" t="n">
         <v>472500</v>
       </c>
-      <c r="H8" s="15" t="n">
+      <c r="H8" s="7" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -2777,7 +2890,7 @@
       <c r="G9" s="7" t="n">
         <v>113500</v>
       </c>
-      <c r="H9" s="15" t="n">
+      <c r="H9" s="7" t="n">
         <v>0.135</v>
       </c>
     </row>
@@ -2811,7 +2924,7 @@
       <c r="G10" s="7" t="n">
         <v>1486500</v>
       </c>
-      <c r="H10" s="15" t="n">
+      <c r="H10" s="7" t="n">
         <v>0.01225740551583248</v>
       </c>
     </row>
@@ -2845,7 +2958,7 @@
       <c r="G11" s="7" t="n">
         <v>54750</v>
       </c>
-      <c r="H11" s="16" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2881,7 +2994,7 @@
       <c r="G12" s="7" t="n">
         <v>15000</v>
       </c>
-      <c r="H12" s="16" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>

--- a/accountant-skill/data/output/Jan2026/adjusting_entries_Jan2026.xlsx
+++ b/accountant-skill/data/output/Jan2026/adjusting_entries_Jan2026.xlsx
@@ -112,7 +112,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -129,42 +129,11 @@
     <border>
       <bottom style="double"/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <bottom style="medium"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -203,33 +172,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -597,17 +539,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -638,9 +580,6 @@
           <t>ENTRIES BY TYPE</t>
         </is>
       </c>
-      <c r="B5" s="17" t="n"/>
-      <c r="C5" s="17" t="n"/>
-      <c r="D5" s="18" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -670,10 +609,10 @@
           <t>Depreciation</t>
         </is>
       </c>
-      <c r="B7" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" s="19" t="n">
+      <c r="B7" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" s="7" t="n">
         <v>54750</v>
       </c>
       <c r="D7" s="7" t="n">
@@ -686,10 +625,10 @@
           <t>Bank Recon</t>
         </is>
       </c>
-      <c r="B8" s="19" t="n">
+      <c r="B8" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="19" t="n">
+      <c r="C8" s="7" t="n">
         <v>33000</v>
       </c>
       <c r="D8" s="7" t="n">
@@ -697,103 +636,88 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="B9" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="C9" s="21" t="n">
+      <c r="B9" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" s="9" t="n">
         <v>87750</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>87750</v>
       </c>
-      <c r="E9" s="22" t="n"/>
-      <c r="F9" s="22" t="n"/>
-      <c r="G9" s="22" t="n"/>
-      <c r="H9" s="22" t="n"/>
     </row>
     <row r="10"/>
     <row r="11">
-      <c r="A11" s="23" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>VALIDATION</t>
         </is>
       </c>
-      <c r="B11" s="17" t="n"/>
-      <c r="C11" s="17" t="n"/>
-      <c r="D11" s="18" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="24" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>Total Debits = Total Credits</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>87,750.00 = 87,750.00</t>
         </is>
       </c>
-      <c r="C13" s="25" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="D13" s="8" t="n"/>
-      <c r="E13" s="22" t="n"/>
-      <c r="F13" s="22" t="n"/>
-      <c r="G13" s="22" t="n"/>
-      <c r="H13" s="22" t="n"/>
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" s="23" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>ALL ENTRIES</t>
         </is>
       </c>
-      <c r="B15" s="17" t="n"/>
-      <c r="C15" s="17" t="n"/>
-      <c r="D15" s="18" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="24" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Reference</t>
         </is>
       </c>
-      <c r="B16" s="24" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D16" s="24" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
@@ -856,7 +780,7 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>13500</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="20">
@@ -867,16 +791,16 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Bank Recon</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Bank recon adj — Bank interest earned</t>
+          <t>Monthly SL depreciation — Office Equipment</t>
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>15000</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="21">
@@ -892,10 +816,30 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
+          <t>Bank recon adj — Bank interest earned</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>ADJ-006</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Bank Recon</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
           <t>Bank recon adj — Software subscription (auto-debit)</t>
         </is>
       </c>
-      <c r="D21" s="7" t="n">
+      <c r="D22" s="7" t="n">
         <v>18000</v>
       </c>
     </row>
@@ -919,16 +863,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
@@ -958,71 +902,64 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>PER-ASSET DETAIL</t>
         </is>
       </c>
-      <c r="B5" s="17" t="n"/>
-      <c r="C5" s="17" t="n"/>
-      <c r="D5" s="17" t="n"/>
-      <c r="E5" s="17" t="n"/>
-      <c r="F5" s="17" t="n"/>
-      <c r="G5" s="17" t="n"/>
-      <c r="H5" s="18" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Asset ID</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="E6" s="24" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Cost</t>
         </is>
       </c>
-      <c r="F6" s="24" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Salvage Value</t>
         </is>
       </c>
-      <c r="G6" s="24" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Useful Life (yrs)</t>
         </is>
       </c>
-      <c r="H6" s="24" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>Annual Depr.</t>
         </is>
       </c>
-      <c r="I6" s="24" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>Monthly Depr.</t>
         </is>
       </c>
-      <c r="J6" s="24" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Depr. Account</t>
         </is>
       </c>
-      <c r="K6" s="24" t="inlineStr">
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>Accum. Depr. Account</t>
         </is>
@@ -1353,7 +1290,7 @@
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>15310</t>
+          <t>15410</t>
         </is>
       </c>
     </row>
@@ -1400,19 +1337,19 @@
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>15310</t>
+          <t>15410</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="20" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>Total Monthly Depreciation</t>
         </is>
       </c>
-      <c r="B15" s="26" t="n"/>
-      <c r="C15" s="26" t="n"/>
-      <c r="D15" s="26" t="n"/>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
       <c r="E15" s="9" t="n"/>
       <c r="F15" s="9" t="n"/>
       <c r="G15" s="9" t="n"/>
@@ -1420,67 +1357,58 @@
       <c r="I15" s="9" t="n">
         <v>54750</v>
       </c>
-      <c r="J15" s="22" t="n"/>
-      <c r="K15" s="22" t="n"/>
     </row>
     <row r="16"/>
     <row r="17"/>
     <row r="18">
-      <c r="A18" s="23" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>JOURNAL ENTRIES (grouped by asset category)</t>
         </is>
       </c>
-      <c r="B18" s="17" t="n"/>
-      <c r="C18" s="17" t="n"/>
-      <c r="D18" s="17" t="n"/>
-      <c r="E18" s="17" t="n"/>
-      <c r="F18" s="17" t="n"/>
-      <c r="G18" s="17" t="n"/>
-      <c r="H18" s="18" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="24" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Reference</t>
         </is>
       </c>
-      <c r="B19" s="24" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C19" s="24" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D19" s="24" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Debit Account</t>
         </is>
       </c>
-      <c r="E19" s="24" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>Dr Code</t>
         </is>
       </c>
-      <c r="F19" s="24" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>Debit Amount</t>
         </is>
       </c>
-      <c r="G19" s="24" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>Credit Account</t>
         </is>
       </c>
-      <c r="H19" s="24" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>Cr Code</t>
         </is>
       </c>
-      <c r="I19" s="24" t="inlineStr">
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>Credit Amount</t>
         </is>
@@ -1599,7 +1527,7 @@
         </is>
       </c>
       <c r="F22" s="7" t="n">
-        <v>13500</v>
+        <v>6000</v>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
@@ -1612,29 +1540,70 @@
         </is>
       </c>
       <c r="I22" s="7" t="n">
-        <v>13500</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="20" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>ADJ-004</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Depreciation — Office Equipment</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Depreciation Expense</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>66000</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>7500</v>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Accum. Depr. — Electrical &amp; Utility Systems</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>15410</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="n">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>Total Depreciation</t>
         </is>
       </c>
-      <c r="B23" s="26" t="n"/>
-      <c r="C23" s="26" t="n"/>
-      <c r="D23" s="26" t="n"/>
-      <c r="E23" s="9" t="n"/>
-      <c r="F23" s="9" t="n">
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="9" t="n">
         <v>54750</v>
       </c>
-      <c r="G23" s="9" t="n"/>
-      <c r="H23" s="9" t="n"/>
-      <c r="I23" s="9" t="n">
+      <c r="G24" s="9" t="n"/>
+      <c r="H24" s="9" t="n"/>
+      <c r="I24" s="9" t="n">
         <v>54750</v>
       </c>
-      <c r="J23" s="22" t="n"/>
-      <c r="K23" s="22" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1658,15 +1627,15 @@
   <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -1747,7 +1716,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>ADJ-004</t>
+          <t>ADJ-005</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -1795,7 +1764,7 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>ADJ-005</t>
+          <t>ADJ-006</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -1841,21 +1810,21 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B8" s="26" t="n"/>
-      <c r="C8" s="26" t="n"/>
-      <c r="D8" s="26" t="n"/>
-      <c r="E8" s="26" t="n"/>
-      <c r="F8" s="26" t="n"/>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
       <c r="G8" s="9" t="n">
         <v>33000</v>
       </c>
-      <c r="H8" s="26" t="n"/>
-      <c r="I8" s="26" t="n"/>
+      <c r="H8" s="9" t="n"/>
+      <c r="I8" s="9" t="n"/>
       <c r="J8" s="9" t="n">
         <v>33000</v>
       </c>
@@ -1880,14 +1849,14 @@
   <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2016,20 +1985,19 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B10" s="26" t="n"/>
+      <c r="B10" s="9" t="n"/>
       <c r="C10" s="9" t="n"/>
-      <c r="D10" s="26" t="n"/>
-      <c r="E10" s="26" t="n"/>
-      <c r="F10" s="26" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="9" t="n"/>
       <c r="G10" s="9" t="n">
         <v>205000</v>
       </c>
-      <c r="H10" s="22" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2052,14 +2020,14 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2159,20 +2127,19 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B9" s="26" t="n"/>
+      <c r="B9" s="9" t="n"/>
       <c r="C9" s="9" t="n"/>
-      <c r="D9" s="26" t="n"/>
-      <c r="E9" s="26" t="n"/>
-      <c r="F9" s="26" t="n"/>
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="9" t="n"/>
       <c r="G9" s="9" t="n">
         <v>20000</v>
       </c>
-      <c r="H9" s="22" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2194,16 +2161,6 @@
   </sheetPr>
   <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -2226,22 +2183,15 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Materials issued to production are recorded via inventory sub-ledgers. Cost of materials used flows to COGS accounts.</t>
         </is>
       </c>
-      <c r="B5" s="17" t="n"/>
-      <c r="C5" s="17" t="n"/>
-      <c r="D5" s="17" t="n"/>
-      <c r="E5" s="17" t="n"/>
-      <c r="F5" s="18" t="n"/>
-    </row>
-    <row r="6"/>
+    </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>No inventory sub-ledger data found for this period.</t>
         </is>
@@ -2265,20 +2215,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="29" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="52" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2498,7 +2448,7 @@
         </is>
       </c>
       <c r="G8" s="7" t="n">
-        <v>13500</v>
+        <v>6000</v>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
@@ -2511,7 +2461,7 @@
         </is>
       </c>
       <c r="J8" s="7" t="n">
-        <v>13500</v>
+        <v>6000</v>
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
@@ -2532,43 +2482,43 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Bank Recon</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Bank Interest Earned</t>
+          <t>Depreciation — Office Equipment</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Cash at Bank</t>
+          <t>Depreciation Expense</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>10100</t>
+          <t>66000</t>
         </is>
       </c>
       <c r="G9" s="7" t="n">
-        <v>15000</v>
+        <v>7500</v>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Interest Income</t>
+          <t>Accum. Depr. — Electrical &amp; Utility Systems</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>15410</t>
         </is>
       </c>
       <c r="J9" s="7" t="n">
-        <v>15000</v>
+        <v>7500</v>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>Bank recon adj — Bank interest earned</t>
+          <t>Monthly SL depreciation — Office Equipment</t>
         </is>
       </c>
     </row>
@@ -2590,75 +2540,128 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
+          <t>Bank Interest Earned</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Cash at Bank</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>10100</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>15000</v>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Interest Income</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>70000</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="n">
+        <v>15000</v>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>Bank recon adj — Bank interest earned</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>ADJ-006</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Bank Recon</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
           <t>Software / Subscription</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>Telephone &amp; Internet</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>65000</t>
         </is>
       </c>
-      <c r="G10" s="7" t="n">
+      <c r="G11" s="7" t="n">
         <v>18000</v>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>Cash at Bank</t>
         </is>
       </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>10100</t>
         </is>
       </c>
-      <c r="J10" s="7" t="n">
+      <c r="J11" s="7" t="n">
         <v>18000</v>
       </c>
-      <c r="K10" s="6" t="inlineStr">
+      <c r="K11" s="6" t="inlineStr">
         <is>
           <t>Bank recon adj — Software subscription (auto-debit)</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="20" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>TOTALS</t>
         </is>
       </c>
-      <c r="B11" s="26" t="n"/>
-      <c r="C11" s="26" t="n"/>
-      <c r="D11" s="26" t="n"/>
-      <c r="E11" s="26" t="n"/>
-      <c r="F11" s="26" t="n"/>
-      <c r="G11" s="9" t="n">
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="9" t="n"/>
+      <c r="E12" s="9" t="n"/>
+      <c r="F12" s="9" t="n"/>
+      <c r="G12" s="9" t="n">
         <v>87750</v>
       </c>
-      <c r="H11" s="26" t="n"/>
-      <c r="I11" s="26" t="n"/>
-      <c r="J11" s="9" t="n">
+      <c r="H12" s="9" t="n"/>
+      <c r="I12" s="9" t="n"/>
+      <c r="J12" s="9" t="n">
         <v>87750</v>
       </c>
-      <c r="K11" s="26" t="n"/>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="K12" s="9" t="n"/>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>Double-Entry Check</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F14" s="10" t="inlineStr">
         <is>
           <t>Dr 87,750.00 = Cr 87,750.00</t>
         </is>
       </c>
-      <c r="G13" s="27" t="inlineStr">
+      <c r="G14" s="11" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2681,17 +2684,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2788,7 +2791,7 @@
       <c r="G6" s="7" t="n">
         <v>1435500</v>
       </c>
-      <c r="H6" s="14" t="n">
+      <c r="H6" s="15" t="n">
         <v>-0.002085505735140772</v>
       </c>
     </row>
@@ -2822,7 +2825,7 @@
       <c r="G7" s="7" t="n">
         <v>518750</v>
       </c>
-      <c r="H7" s="7" t="n">
+      <c r="H7" s="15" t="n">
         <v>0.0375</v>
       </c>
     </row>
@@ -2856,7 +2859,7 @@
       <c r="G8" s="7" t="n">
         <v>472500</v>
       </c>
-      <c r="H8" s="7" t="n">
+      <c r="H8" s="15" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -2882,61 +2885,61 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>100000</v>
+        <v>160000</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>13500</v>
+        <v>6000</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>113500</v>
-      </c>
-      <c r="H9" s="7" t="n">
-        <v>0.135</v>
+        <v>166000</v>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>0.0375</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>65000</t>
+          <t>15410</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Factory Buildings &amp; Office Supplies and Maintenance</t>
+          <t>Accumulated Depreciation - Electrical &amp; Utility Systems</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1468500</v>
+        <v>100000</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>18000</v>
+        <v>7500</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>1486500</v>
-      </c>
-      <c r="H10" s="7" t="n">
-        <v>0.01225740551583248</v>
+        <v>107500</v>
+      </c>
+      <c r="H10" s="15" t="n">
+        <v>0.075</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>66000</t>
+          <t>65000</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Depreciation Expenses - SG&amp;A</t>
+          <t>Factory Buildings &amp; Office Supplies and Maintenance</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -2950,51 +2953,85 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>0</v>
+        <v>45000</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>54750</v>
+        <v>18000</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>54750</v>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>63000</v>
+      </c>
+      <c r="H11" s="15" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>66000</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Interest Income</t>
+          <t>Depreciation Expenses - SG&amp;A</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="E12" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="7" t="n">
+        <v>54750</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>54750</v>
+      </c>
+      <c r="H12" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>70000</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Interest Income</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="7" t="n">
         <v>15000</v>
       </c>
-      <c r="G12" s="7" t="n">
+      <c r="G13" s="7" t="n">
         <v>15000</v>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H13" s="16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
